--- a/outputs/daily/hr_rankings_2026-08-21_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-21_full.xlsx
@@ -11766,34 +11766,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14810,34 +14806,30 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24966,34 +24958,30 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30386,34 +30374,30 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32602,34 +32586,30 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36402,34 +36382,30 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -55870,34 +55846,30 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -61850,34 +61822,30 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB225" t="inlineStr"/>
       <c r="AC225" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -68998,34 +68966,30 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB251" t="inlineStr"/>
       <c r="AC251" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
